--- a/data/entity_financials.xlsx
+++ b/data/entity_financials.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Financials" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Financials" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -477,19 +477,19 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>455491.91</v>
+        <v>427142.77</v>
       </c>
       <c r="D2" t="n">
-        <v>394047.67</v>
+        <v>363610.23</v>
       </c>
       <c r="E2" t="n">
-        <v>49635.92</v>
+        <v>46338.25</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>15452.26</v>
+        <v>12667.56</v>
       </c>
     </row>
     <row r="3">
@@ -504,19 +504,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>445521.63</v>
+        <v>440470.48</v>
       </c>
       <c r="D3" t="n">
-        <v>380087.42</v>
+        <v>376635.74</v>
       </c>
       <c r="E3" t="n">
-        <v>40365.04</v>
+        <v>36864.39</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>9490.959999999999</v>
+        <v>11064.22</v>
       </c>
     </row>
     <row r="4">
@@ -531,19 +531,19 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>456674.42</v>
+        <v>467792.96</v>
       </c>
       <c r="D4" t="n">
-        <v>394614.37</v>
+        <v>404422.3</v>
       </c>
       <c r="E4" t="n">
-        <v>40689.99</v>
+        <v>38304.04</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>9246.59</v>
+        <v>10775.15</v>
       </c>
     </row>
     <row r="5">
@@ -558,19 +558,19 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>365146.45</v>
+        <v>365440.23</v>
       </c>
       <c r="D5" t="n">
-        <v>309406.33</v>
+        <v>309022.1</v>
       </c>
       <c r="E5" t="n">
-        <v>32288.06</v>
+        <v>34303.42</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>9174.790000000001</v>
+        <v>7461.85</v>
       </c>
     </row>
     <row r="6">
@@ -585,19 +585,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>703849.45</v>
+        <v>797329.01</v>
       </c>
       <c r="D6" t="n">
-        <v>607692.2</v>
+        <v>686375.8100000001</v>
       </c>
       <c r="E6" t="n">
-        <v>27702.02</v>
+        <v>29620.59</v>
       </c>
       <c r="F6" t="n">
-        <v>10545.05</v>
+        <v>12020.93</v>
       </c>
       <c r="G6" t="n">
-        <v>17637.29</v>
+        <v>16053.28</v>
       </c>
     </row>
     <row r="7">
@@ -612,19 +612,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1533568.09</v>
+        <v>1440994</v>
       </c>
       <c r="D7" t="n">
-        <v>801317.62</v>
+        <v>997137.29</v>
       </c>
       <c r="E7" t="n">
-        <v>107003.81</v>
+        <v>89296.92999999999</v>
       </c>
       <c r="F7" t="n">
-        <v>316663.2</v>
+        <v>70903.75999999999</v>
       </c>
       <c r="G7" t="n">
-        <v>41965.15</v>
+        <v>32435.15</v>
       </c>
     </row>
   </sheetData>

--- a/data/entity_financials.xlsx
+++ b/data/entity_financials.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Financials" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Financials" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
